--- a/sum_daily_order/result/Weekly_Performance_Report_JP.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,22 +42,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>All order-2026-01-21-18_42.csv</t>
-  </si>
-  <si>
-    <t>All order-2026-01-21-18_41.csv</t>
-  </si>
-  <si>
-    <t>All order-2026-01-22-18_49.csv</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
+    <t>全部 笔订单-2026-01-25-22_29.csv</t>
+  </si>
+  <si>
+    <t>全部 笔订单-2026-01-25-22_48.csv</t>
+  </si>
+  <si>
+    <t>2026-01-25</t>
+  </si>
+  <si>
+    <t>2026-01-18</t>
   </si>
   <si>
     <t>日期</t>
@@ -81,13 +75,25 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>电动剃眉刀</t>
-  </si>
-  <si>
-    <t>车载手机支架</t>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>电动鼻毛刀</t>
+  </si>
+  <si>
+    <t>蓝牙MP3</t>
+  </si>
+  <si>
+    <t>头发护理精华</t>
+  </si>
+  <si>
+    <t>车载充电器</t>
   </si>
   <si>
     <t>产品名称</t>
+  </si>
+  <si>
+    <t>ワイヤレス翻訳ヘッドフォンは、Bluetooth 5.4、オープンイヤークリップデザインを特徴とし、マイク、ENCコールノイズキャンセル、デジタルLEDディスプレイ、残り容量、およびiOS/Androidのサポートを備えています</t>
   </si>
   <si>
     <t>汇总</t>
@@ -430,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -464,25 +470,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>3190</v>
+        <v>80319</v>
       </c>
       <c r="D2">
-        <v>159.5</v>
+        <v>4015.95</v>
       </c>
       <c r="E2">
-        <v>3190</v>
+        <v>55585</v>
       </c>
       <c r="F2">
-        <v>13.8</v>
+        <v>611.8</v>
       </c>
       <c r="G2">
-        <v>42.5</v>
+        <v>1613.51</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>33.89</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -490,51 +496,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>5400</v>
+        <v>31437</v>
       </c>
       <c r="D3">
-        <v>270</v>
+        <v>1571.85</v>
       </c>
       <c r="E3">
-        <v>5340</v>
+        <v>22068</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>245.4</v>
       </c>
       <c r="G3">
-        <v>62.5</v>
+        <v>601.09</v>
       </c>
       <c r="H3">
-        <v>39.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>2060</v>
-      </c>
-      <c r="D4">
-        <v>103</v>
-      </c>
-      <c r="E4">
-        <v>2060</v>
-      </c>
-      <c r="F4">
-        <v>4.6</v>
-      </c>
-      <c r="G4">
-        <v>17.5</v>
-      </c>
-      <c r="H4">
-        <v>39.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -544,33 +524,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
         <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -578,22 +558,22 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>2160</v>
+        <v>4349</v>
       </c>
       <c r="D2">
-        <v>108</v>
+        <v>217.45</v>
       </c>
       <c r="E2">
-        <v>2160</v>
+        <v>3999</v>
       </c>
       <c r="F2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -604,22 +584,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>1030</v>
+        <v>25047</v>
       </c>
       <c r="D3">
-        <v>51.5</v>
+        <v>1252.35</v>
       </c>
       <c r="E3">
-        <v>1030</v>
+        <v>16716</v>
       </c>
       <c r="F3">
-        <v>4.6</v>
+        <v>202.4</v>
       </c>
       <c r="G3">
-        <v>17.5</v>
+        <v>577.0700000000001</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -627,36 +607,36 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4">
-        <v>5400</v>
+        <v>2041</v>
       </c>
       <c r="D4">
-        <v>270</v>
+        <v>102.05</v>
       </c>
       <c r="E4">
-        <v>5340</v>
+        <v>1353</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>62.5</v>
+        <v>24.02</v>
       </c>
       <c r="H4">
-        <v>17.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -674,59 +654,111 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>22.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>9399</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>469.95</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>7099</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>110.8</v>
       </c>
       <c r="H6">
-        <v>17.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>2060</v>
+        <v>66788</v>
       </c>
       <c r="D7">
-        <v>103</v>
+        <v>3339.4</v>
       </c>
       <c r="E7">
-        <v>2060</v>
+        <v>45381</v>
       </c>
       <c r="F7">
-        <v>4.6</v>
+        <v>510.4</v>
       </c>
       <c r="G7">
-        <v>17.5</v>
+        <v>1455.22</v>
       </c>
       <c r="H7">
-        <v>22.1</v>
+        <v>33.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>2026</v>
+      </c>
+      <c r="D8">
+        <v>101.3</v>
+      </c>
+      <c r="E8">
+        <v>1676</v>
+      </c>
+      <c r="F8">
+        <v>43</v>
+      </c>
+      <c r="G8">
+        <v>24.02</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9">
+        <v>2106</v>
+      </c>
+      <c r="D9">
+        <v>105.3</v>
+      </c>
+      <c r="E9">
+        <v>1429</v>
+      </c>
+      <c r="F9">
+        <v>18.4</v>
+      </c>
+      <c r="G9">
+        <v>23.47</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -736,63 +768,84 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>58</v>
+      </c>
+      <c r="C2">
         <v>23</v>
       </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="1" customFormat="1">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5">
         <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="1" customFormat="1">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1">
+        <v>64</v>
+      </c>
+      <c r="C7" s="1">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,16 +42,10 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>全部 笔订单-2026-01-25-22_29.csv</t>
-  </si>
-  <si>
-    <t>全部 笔订单-2026-01-25-22_48.csv</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
+    <t>All order-2026-02-10-08_54.csv</t>
+  </si>
+  <si>
+    <t>2026-02-09</t>
   </si>
   <si>
     <t>日期</t>
@@ -75,25 +69,13 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>电动鼻毛刀</t>
-  </si>
-  <si>
-    <t>蓝牙MP3</t>
-  </si>
-  <si>
-    <t>头发护理精华</t>
-  </si>
-  <si>
-    <t>车载充电器</t>
+    <t>电动剃眉刀</t>
+  </si>
+  <si>
+    <t>车载手机支架</t>
   </si>
   <si>
     <t>产品名称</t>
-  </si>
-  <si>
-    <t>ワイヤレス翻訳ヘッドフォンは、Bluetooth 5.4、オープンイヤークリップデザインを特徴とし、マイク、ENCコールノイズキャンセル、デジタルLEDディスプレイ、残り容量、およびiOS/Androidのサポートを備えています</t>
   </si>
   <si>
     <t>汇总</t>
@@ -103,8 +85,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -127,7 +117,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -135,13 +125,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,32 +444,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -470,50 +478,24 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>80319</v>
+        <v>5752</v>
       </c>
       <c r="D2">
-        <v>4015.95</v>
+        <v>287.6</v>
       </c>
       <c r="E2">
-        <v>55585</v>
+        <v>5752</v>
       </c>
       <c r="F2">
-        <v>611.8</v>
+        <v>27.6</v>
       </c>
       <c r="G2">
-        <v>1613.51</v>
+        <v>95</v>
       </c>
       <c r="H2">
-        <v>33.89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>31437</v>
-      </c>
-      <c r="D3">
-        <v>1571.85</v>
-      </c>
-      <c r="E3">
-        <v>22068</v>
-      </c>
-      <c r="F3">
-        <v>245.4</v>
-      </c>
-      <c r="G3">
-        <v>601.09</v>
-      </c>
-      <c r="H3">
         <v>0</v>
       </c>
     </row>
@@ -524,56 +506,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>4349</v>
+        <v>2160</v>
       </c>
       <c r="D2">
-        <v>217.45</v>
+        <v>108</v>
       </c>
       <c r="E2">
-        <v>3999</v>
+        <v>2160</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -581,183 +563,27 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>25047</v>
+        <v>3592</v>
       </c>
       <c r="D3">
-        <v>1252.35</v>
+        <v>179.6</v>
       </c>
       <c r="E3">
-        <v>16716</v>
+        <v>3592</v>
       </c>
       <c r="F3">
-        <v>202.4</v>
+        <v>18.4</v>
       </c>
       <c r="G3">
-        <v>577.0700000000001</v>
+        <v>70</v>
       </c>
       <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4">
-        <v>2041</v>
-      </c>
-      <c r="D4">
-        <v>102.05</v>
-      </c>
-      <c r="E4">
-        <v>1353</v>
-      </c>
-      <c r="F4">
-        <v>43</v>
-      </c>
-      <c r="G4">
-        <v>24.02</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6">
-        <v>9399</v>
-      </c>
-      <c r="D6">
-        <v>469.95</v>
-      </c>
-      <c r="E6">
-        <v>7099</v>
-      </c>
-      <c r="F6">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <v>110.8</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>66788</v>
-      </c>
-      <c r="D7">
-        <v>3339.4</v>
-      </c>
-      <c r="E7">
-        <v>45381</v>
-      </c>
-      <c r="F7">
-        <v>510.4</v>
-      </c>
-      <c r="G7">
-        <v>1455.22</v>
-      </c>
-      <c r="H7">
-        <v>33.89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8">
-        <v>2026</v>
-      </c>
-      <c r="D8">
-        <v>101.3</v>
-      </c>
-      <c r="E8">
-        <v>1676</v>
-      </c>
-      <c r="F8">
-        <v>43</v>
-      </c>
-      <c r="G8">
-        <v>24.02</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9">
-        <v>2106</v>
-      </c>
-      <c r="D9">
-        <v>105.3</v>
-      </c>
-      <c r="E9">
-        <v>1429</v>
-      </c>
-      <c r="F9">
-        <v>18.4</v>
-      </c>
-      <c r="G9">
-        <v>23.47</v>
-      </c>
-      <c r="H9">
         <v>0</v>
       </c>
     </row>
@@ -768,84 +594,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="2" customFormat="1">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2">
-        <v>58</v>
-      </c>
-      <c r="C2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="1" customFormat="1">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="1">
-        <v>64</v>
-      </c>
-      <c r="C7" s="1">
-        <v>25</v>
+      <c r="B4" s="2">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,10 +42,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>All order-2026-02-10-08_54.csv</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
+    <t>全部 笔订单-2026-02-26-10_51.csv</t>
+  </si>
+  <si>
+    <t>全部 笔订单-2026-02-26-10_52.csv</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
   </si>
   <si>
     <t>日期</t>
@@ -69,10 +75,10 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>电动剃眉刀</t>
-  </si>
-  <si>
-    <t>车载手机支架</t>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>电动鼻毛刀</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -444,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -478,25 +484,51 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>9373</v>
+      </c>
+      <c r="D2">
+        <v>468.65</v>
+      </c>
+      <c r="E2">
+        <v>6923</v>
+      </c>
+      <c r="F2">
+        <v>61.6</v>
+      </c>
+      <c r="G2">
+        <v>192.5</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>5752</v>
-      </c>
-      <c r="D2">
-        <v>287.6</v>
-      </c>
-      <c r="E2">
-        <v>5752</v>
-      </c>
-      <c r="F2">
-        <v>27.6</v>
-      </c>
-      <c r="G2">
-        <v>95</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>14729</v>
+      </c>
+      <c r="D3">
+        <v>736.45</v>
+      </c>
+      <c r="E3">
+        <v>10286</v>
+      </c>
+      <c r="F3">
+        <v>96.8</v>
+      </c>
+      <c r="G3">
+        <v>302.5</v>
+      </c>
+      <c r="H3">
+        <v>326.7</v>
       </c>
     </row>
   </sheetData>
@@ -506,56 +538,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>2160</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2160</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -563,28 +595,80 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>3592</v>
+        <v>9373</v>
       </c>
       <c r="D3">
-        <v>179.6</v>
+        <v>468.65</v>
       </c>
       <c r="E3">
-        <v>3592</v>
+        <v>6923</v>
       </c>
       <c r="F3">
-        <v>18.4</v>
+        <v>61.60000000000001</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>192.5</v>
       </c>
       <c r="H3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>14729</v>
+      </c>
+      <c r="D5">
+        <v>736.45</v>
+      </c>
+      <c r="E5">
+        <v>10286</v>
+      </c>
+      <c r="F5">
+        <v>96.80000000000001</v>
+      </c>
+      <c r="G5">
+        <v>302.5</v>
+      </c>
+      <c r="H5">
+        <v>326.7</v>
       </c>
     </row>
   </sheetData>
@@ -594,39 +678,40 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="2" customFormat="1">
       <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="2" customFormat="1">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>6</v>
+        <v>22</v>
+      </c>
+      <c r="B3" s="2">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
